--- a/Config/GameConfig/Datas/farmlandUnlock.xlsx
+++ b/Config/GameConfig/Datas/farmlandUnlock.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Configs\GameConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9318890D-908D-4256-A21F-20B809B9E0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286678AC-1121-40AD-A35C-42A3DF61CDC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -139,10 +139,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>array,item.ItemExchange</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>1000001,50</t>
   </si>
   <si>
@@ -183,6 +179,10 @@
   </si>
   <si>
     <t>cost</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>list,item.ItemExchange</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -410,6 +410,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -434,7 +435,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="差" xfId="2" builtinId="27"/>
@@ -741,10 +741,10 @@
       <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="5"/>
+      <c r="E1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="6"/>
       <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
@@ -756,8 +756,8 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -773,10 +773,10 @@
       <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="9"/>
+      <c r="E3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="10"/>
       <c r="G3" s="2" t="s">
         <v>4</v>
       </c>
@@ -788,8 +788,8 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="12"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -805,17 +805,17 @@
       <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="5"/>
+      <c r="F5" s="6"/>
       <c r="G5" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6">
-        <v>1210001</v>
+        <v>10001</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>11</v>
@@ -823,11 +823,11 @@
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>23</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -835,7 +835,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7">
-        <v>1210002</v>
+        <v>10002</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>16</v>
@@ -843,11 +843,11 @@
       <c r="D7">
         <v>2</v>
       </c>
-      <c r="E7" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="12" t="s">
+      <c r="E7" s="4" t="s">
         <v>24</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -855,7 +855,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8">
-        <v>1210003</v>
+        <v>10003</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>17</v>
@@ -863,11 +863,11 @@
       <c r="D8">
         <v>3</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>26</v>
+      <c r="E8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="G8">
         <v>7</v>
@@ -875,7 +875,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9">
-        <v>1210004</v>
+        <v>10004</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>18</v>
@@ -883,11 +883,11 @@
       <c r="D9">
         <v>4</v>
       </c>
-      <c r="E9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>27</v>
+      <c r="E9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B10">
-        <v>1210005</v>
+        <v>10005</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>19</v>
@@ -903,127 +903,127 @@
       <c r="D10">
         <v>5</v>
       </c>
-      <c r="E10" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>28</v>
+      <c r="E10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="G10">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
     </row>
     <row r="17" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
     </row>
     <row r="18" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
     </row>
     <row r="19" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
     </row>
     <row r="20" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
     </row>
     <row r="21" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
     </row>
     <row r="22" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
     </row>
     <row r="23" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
     </row>
     <row r="24" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
     </row>
     <row r="25" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
     </row>
     <row r="26" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
     </row>
     <row r="27" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
     </row>
     <row r="28" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
     </row>
     <row r="29" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
     </row>
     <row r="30" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
     </row>
     <row r="31" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
     </row>
     <row r="32" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
     </row>
     <row r="33" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
     </row>
     <row r="34" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
     </row>
     <row r="35" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
     </row>
     <row r="36" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
     </row>
     <row r="37" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
     </row>
     <row r="38" spans="5:6" x14ac:dyDescent="0.2">
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="5">
